--- a/state/3800_sint-truiden.xlsx
+++ b/state/3800_sint-truiden.xlsx
@@ -3816,6 +3816,16 @@
           <t>N</t>
         </is>
       </c>
+      <c r="ES5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="ET5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="EU5" t="inlineStr">
         <is>
           <t>N</t>
@@ -3978,6 +3988,16 @@
           <t>N</t>
         </is>
       </c>
+      <c r="ES6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="ET6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="EU6" t="inlineStr">
         <is>
           <t>N</t>
@@ -4140,6 +4160,16 @@
           <t>N</t>
         </is>
       </c>
+      <c r="ES7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="ET7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="EU7" t="inlineStr">
         <is>
           <t>N</t>
@@ -4302,6 +4332,16 @@
           <t>N</t>
         </is>
       </c>
+      <c r="ES8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="ET8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="EU8" t="inlineStr">
         <is>
           <t>N</t>
@@ -4464,6 +4504,16 @@
           <t>N</t>
         </is>
       </c>
+      <c r="ES9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="ET9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="EU9" t="inlineStr">
         <is>
           <t>N</t>
@@ -4626,6 +4676,16 @@
           <t>N</t>
         </is>
       </c>
+      <c r="ES10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="ET10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="EU10" t="inlineStr">
         <is>
           <t>N</t>
@@ -4784,6 +4844,16 @@
         </is>
       </c>
       <c r="ER11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="ES11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="ET11" t="inlineStr">
         <is>
           <t>N</t>
         </is>

--- a/state/3800_sint-truiden.xlsx
+++ b/state/3800_sint-truiden.xlsx
@@ -3891,6 +3891,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="GE5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="GF5" t="inlineStr">
         <is>
           <t>O</t>
@@ -4063,6 +4068,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="GE6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="GF6" t="inlineStr">
         <is>
           <t>O</t>
@@ -4235,6 +4245,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="GA7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="GF7" t="inlineStr">
         <is>
           <t>O</t>
@@ -4407,6 +4422,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="FZ8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="GF8" t="inlineStr">
         <is>
           <t>O</t>
@@ -4579,6 +4599,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="FZ9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="GF9" t="inlineStr">
         <is>
           <t>O</t>
@@ -4751,6 +4776,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="GA10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="GF10" t="inlineStr">
         <is>
           <t>O</t>
@@ -4921,6 +4951,11 @@
       <c r="FJ11" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="FZ11" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="GF11" t="inlineStr">

--- a/state/3800_sint-truiden.xlsx
+++ b/state/3800_sint-truiden.xlsx
@@ -3786,6 +3786,16 @@
           <t>N</t>
         </is>
       </c>
+      <c r="EJ5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="EK5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="EL5" t="inlineStr">
         <is>
           <t>N</t>
@@ -3963,6 +3973,16 @@
           <t>N</t>
         </is>
       </c>
+      <c r="EJ6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="EK6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="EL6" t="inlineStr">
         <is>
           <t>N</t>
@@ -4140,6 +4160,16 @@
           <t>N</t>
         </is>
       </c>
+      <c r="EJ7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="EK7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="EL7" t="inlineStr">
         <is>
           <t>N</t>
@@ -4317,6 +4347,16 @@
           <t>N</t>
         </is>
       </c>
+      <c r="EJ8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="EK8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="EL8" t="inlineStr">
         <is>
           <t>N</t>
@@ -4494,6 +4534,16 @@
           <t>N</t>
         </is>
       </c>
+      <c r="EJ9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="EK9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="EL9" t="inlineStr">
         <is>
           <t>N</t>
@@ -4671,6 +4721,16 @@
           <t>N</t>
         </is>
       </c>
+      <c r="EJ10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="EK10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="EL10" t="inlineStr">
         <is>
           <t>N</t>
@@ -4844,6 +4904,16 @@
         </is>
       </c>
       <c r="EI11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="EJ11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="EK11" t="inlineStr">
         <is>
           <t>N</t>
         </is>

--- a/state/3800_sint-truiden.xlsx
+++ b/state/3800_sint-truiden.xlsx
@@ -3781,6 +3781,11 @@
           <t>O</t>
         </is>
       </c>
+      <c r="EA5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="EI5" t="inlineStr">
         <is>
           <t>N</t>
@@ -3968,6 +3973,11 @@
           <t>O</t>
         </is>
       </c>
+      <c r="EA6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="EI6" t="inlineStr">
         <is>
           <t>N</t>
@@ -4155,6 +4165,11 @@
           <t>O</t>
         </is>
       </c>
+      <c r="EA7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="EI7" t="inlineStr">
         <is>
           <t>N</t>
@@ -4342,6 +4357,11 @@
           <t>O</t>
         </is>
       </c>
+      <c r="EA8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="EI8" t="inlineStr">
         <is>
           <t>N</t>
@@ -4529,6 +4549,11 @@
           <t>O</t>
         </is>
       </c>
+      <c r="EA9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="EI9" t="inlineStr">
         <is>
           <t>N</t>
@@ -4716,6 +4741,11 @@
           <t>O</t>
         </is>
       </c>
+      <c r="EA10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="EI10" t="inlineStr">
         <is>
           <t>N</t>
@@ -4901,6 +4931,11 @@
       <c r="DW11" t="inlineStr">
         <is>
           <t>O</t>
+        </is>
+      </c>
+      <c r="EA11" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="EI11" t="inlineStr">

--- a/state/3800_sint-truiden.xlsx
+++ b/state/3800_sint-truiden.xlsx
@@ -3806,6 +3806,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="EM5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="EN5" t="inlineStr">
         <is>
           <t>N</t>
@@ -3998,6 +4003,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="EM6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="EN6" t="inlineStr">
         <is>
           <t>N</t>
@@ -4190,6 +4200,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="EM7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="EN7" t="inlineStr">
         <is>
           <t>N</t>
@@ -4382,6 +4397,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="EM8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="EN8" t="inlineStr">
         <is>
           <t>N</t>
@@ -4574,6 +4594,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="EM9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="EN9" t="inlineStr">
         <is>
           <t>N</t>
@@ -4766,6 +4791,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="EM10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="EN10" t="inlineStr">
         <is>
           <t>N</t>
@@ -4954,6 +4984,11 @@
         </is>
       </c>
       <c r="EL11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="EM11" t="inlineStr">
         <is>
           <t>N</t>
         </is>

--- a/state/3800_sint-truiden.xlsx
+++ b/state/3800_sint-truiden.xlsx
@@ -3,10 +3,11 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" tabRatio="600" firstSheet="1" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mesen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feuille" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RUP" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
@@ -16,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="13">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -92,26 +93,22 @@
     <font>
       <name val="Aptos Narrow"/>
       <charset val="1"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Aptos Narrow"/>
-      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <name val="Aptos Narrow"/>
-      <color rgb="FFFF0000"/>
+      <name val="Courier"/>
+      <charset val="1"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color rgb="FF333332"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="70">
@@ -530,7 +527,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -580,9 +577,29 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
       <top/>
       <bottom style="thin">
@@ -596,6 +613,19 @@
         <color indexed="64"/>
       </right>
       <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -618,14 +648,76 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FFCCCCCC"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
       </bottom>
       <diagonal/>
     </border>
@@ -640,18 +732,22 @@
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
@@ -663,30 +759,15 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -731,6 +812,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -996,38 +1080,74 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="60" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="60" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="60" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="29" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="60" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1361,8 +1481,6 @@
   <dimension ref="A1:GG11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="14.5703125" customWidth="1" min="3" max="3"/>
     <col width="11.42578125" customWidth="1" min="6" max="187"/>
   </cols>
   <sheetData>
@@ -1498,7 +1616,7 @@
       <c r="DT1" s="5" t="n"/>
       <c r="DU1" s="5" t="n"/>
       <c r="DV1" s="5" t="n"/>
-      <c r="DW1" s="81" t="n"/>
+      <c r="DW1" s="82" t="n"/>
       <c r="DX1" s="5" t="n"/>
       <c r="DY1" s="5" t="n"/>
       <c r="DZ1" s="5" t="n"/>
@@ -1726,26 +1844,26 @@
           <t>natur et milieu ( milieu)</t>
         </is>
       </c>
-      <c r="DF2" s="115" t="inlineStr">
+      <c r="DF2" s="134" t="inlineStr">
         <is>
           <t>natur et milieu ( milieu)</t>
         </is>
       </c>
-      <c r="DG2" s="128" t="n"/>
-      <c r="DH2" s="128" t="n"/>
-      <c r="DI2" s="128" t="n"/>
-      <c r="DJ2" s="128" t="n"/>
-      <c r="DK2" s="128" t="n"/>
-      <c r="DL2" s="128" t="n"/>
-      <c r="DM2" s="128" t="n"/>
-      <c r="DN2" s="128" t="n"/>
-      <c r="DO2" s="128" t="n"/>
-      <c r="DP2" s="128" t="n"/>
-      <c r="DQ2" s="128" t="n"/>
-      <c r="DR2" s="113" t="n"/>
-      <c r="DS2" s="113" t="n"/>
-      <c r="DT2" s="113" t="n"/>
-      <c r="DU2" s="113" t="n"/>
+      <c r="DG2" s="135" t="n"/>
+      <c r="DH2" s="135" t="n"/>
+      <c r="DI2" s="135" t="n"/>
+      <c r="DJ2" s="135" t="n"/>
+      <c r="DK2" s="135" t="n"/>
+      <c r="DL2" s="135" t="n"/>
+      <c r="DM2" s="135" t="n"/>
+      <c r="DN2" s="135" t="n"/>
+      <c r="DO2" s="135" t="n"/>
+      <c r="DP2" s="135" t="n"/>
+      <c r="DQ2" s="136" t="n"/>
+      <c r="DR2" s="120" t="n"/>
+      <c r="DS2" s="120" t="n"/>
+      <c r="DT2" s="120" t="n"/>
+      <c r="DU2" s="120" t="n"/>
       <c r="DV2" s="17" t="inlineStr">
         <is>
           <t>natur et milieu (WATER)</t>
@@ -1884,7 +2002,7 @@
           <t>Landinrichting</t>
         </is>
       </c>
-      <c r="FA2" s="127" t="inlineStr">
+      <c r="FA2" s="20" t="inlineStr">
         <is>
           <t>Landinrichting
 Ruilverkaveling van landeigendommen uit kracht van wet</t>
@@ -1935,38 +2053,38 @@
           <t>Bouwen en wonen ( Geluidsbelasting)</t>
         </is>
       </c>
-      <c r="FL2" s="20" t="n"/>
-      <c r="FM2" s="20" t="n"/>
-      <c r="FN2" s="20" t="n"/>
-      <c r="FO2" s="20" t="n"/>
+      <c r="FL2" s="21" t="n"/>
+      <c r="FM2" s="21" t="n"/>
+      <c r="FN2" s="21" t="n"/>
+      <c r="FO2" s="21" t="n"/>
       <c r="FP2" s="17" t="inlineStr">
         <is>
           <t>Bouwen en wonen ( Geluidsbelasting)</t>
         </is>
       </c>
-      <c r="FQ2" s="20" t="n"/>
-      <c r="FR2" s="20" t="n"/>
-      <c r="FS2" s="20" t="n"/>
-      <c r="FT2" s="20" t="n"/>
+      <c r="FQ2" s="21" t="n"/>
+      <c r="FR2" s="21" t="n"/>
+      <c r="FS2" s="21" t="n"/>
+      <c r="FT2" s="21" t="n"/>
       <c r="FU2" s="17" t="inlineStr">
         <is>
           <t>Bouwen en wonen ( Geluidsbelasting)</t>
         </is>
       </c>
-      <c r="FV2" s="21" t="n"/>
-      <c r="FW2" s="21" t="n"/>
-      <c r="FX2" s="21" t="n"/>
-      <c r="FY2" s="21" t="n"/>
+      <c r="FV2" s="22" t="n"/>
+      <c r="FW2" s="22" t="n"/>
+      <c r="FX2" s="22" t="n"/>
+      <c r="FY2" s="22" t="n"/>
       <c r="FZ2" s="9" t="inlineStr">
         <is>
           <t>Etat des sols -mj https://www.degrotegrondvraag.be/</t>
         </is>
       </c>
-      <c r="GA2" s="21" t="n"/>
-      <c r="GB2" s="21" t="n"/>
-      <c r="GC2" s="21" t="n"/>
-      <c r="GD2" s="21" t="n"/>
-      <c r="GE2" s="21" t="n"/>
+      <c r="GA2" s="22" t="n"/>
+      <c r="GB2" s="22" t="n"/>
+      <c r="GC2" s="22" t="n"/>
+      <c r="GD2" s="22" t="n"/>
+      <c r="GE2" s="22" t="n"/>
       <c r="GF2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> Code du logement (Bouwen en wonen ,Vlaamse wooncode)</t>
@@ -1974,68 +2092,68 @@
       </c>
       <c r="GG2" s="9" t="n"/>
     </row>
-    <row r="3" ht="50.25" customHeight="1">
-      <c r="A3" s="22" t="n"/>
-      <c r="B3" s="22" t="n"/>
-      <c r="C3" s="23" t="n"/>
-      <c r="D3" s="24" t="n"/>
-      <c r="E3" s="24" t="n"/>
-      <c r="F3" s="25" t="inlineStr">
+    <row r="3" ht="63.75" customHeight="1">
+      <c r="A3" s="23" t="n"/>
+      <c r="B3" s="23" t="n"/>
+      <c r="C3" s="24" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="26" t="inlineStr">
         <is>
           <t>Woongebieden</t>
         </is>
       </c>
-      <c r="G3" s="26" t="inlineStr">
+      <c r="G3" s="27" t="inlineStr">
         <is>
           <t>Woonuitbreidingsgebieden</t>
         </is>
       </c>
-      <c r="H3" s="27" t="inlineStr">
+      <c r="H3" s="28" t="inlineStr">
         <is>
           <t>Woonparken</t>
         </is>
       </c>
-      <c r="I3" s="28" t="inlineStr">
+      <c r="I3" s="29" t="inlineStr">
         <is>
           <t>Woongebieden met een landelijk karakter</t>
         </is>
       </c>
-      <c r="J3" s="25" t="inlineStr">
+      <c r="J3" s="26" t="inlineStr">
         <is>
           <t>Woongebieden met culturelke, historische en/of esthetische waarde</t>
         </is>
       </c>
-      <c r="K3" s="29" t="inlineStr">
+      <c r="K3" s="30" t="inlineStr">
         <is>
           <t>Gebied voor kernontwikkeling</t>
         </is>
       </c>
-      <c r="L3" s="30" t="inlineStr">
+      <c r="L3" s="31" t="inlineStr">
         <is>
           <t>Industriegebieden</t>
         </is>
       </c>
-      <c r="M3" s="30" t="inlineStr">
+      <c r="M3" s="31" t="inlineStr">
         <is>
           <t>Gebieden voor vervuilende industrieën</t>
         </is>
       </c>
-      <c r="N3" s="30" t="inlineStr">
+      <c r="N3" s="31" t="inlineStr">
         <is>
           <t>Gebieden voor milieubelastende industrieën</t>
         </is>
       </c>
-      <c r="O3" s="31" t="inlineStr">
+      <c r="O3" s="32" t="inlineStr">
         <is>
           <t>Gebieden voor ambachtelijke bedrijven en de gebieden voor kleine en middelgrote ondernemingen</t>
         </is>
       </c>
-      <c r="P3" s="32" t="inlineStr">
+      <c r="P3" s="33" t="inlineStr">
         <is>
           <t>Dienstverleningsgebieden (D)</t>
         </is>
       </c>
-      <c r="Q3" s="32" t="inlineStr">
+      <c r="Q3" s="33" t="inlineStr">
         <is>
           <t>Gebieden hoofdzakelijk besteld voor de vestiging van grootwinkelbedrijven</t>
         </is>
@@ -2045,592 +2163,592 @@
           <t>Landelijke gebieden</t>
         </is>
       </c>
-      <c r="S3" s="33" t="inlineStr">
+      <c r="S3" s="34" t="inlineStr">
         <is>
           <t>Agrarische gebieden</t>
         </is>
       </c>
-      <c r="T3" s="34" t="inlineStr">
+      <c r="T3" s="35" t="inlineStr">
         <is>
           <t>Bosgebieden</t>
         </is>
       </c>
-      <c r="U3" s="35" t="inlineStr">
+      <c r="U3" s="36" t="inlineStr">
         <is>
           <t>Groengebieden</t>
         </is>
       </c>
-      <c r="V3" s="35" t="inlineStr">
+      <c r="V3" s="36" t="inlineStr">
         <is>
           <t>Natuurgebieden (N)</t>
         </is>
       </c>
-      <c r="W3" s="35" t="inlineStr">
+      <c r="W3" s="36" t="inlineStr">
         <is>
           <t>Natuurgebieden met wetenschappelijke waarde of natuurreservaten ®</t>
         </is>
       </c>
-      <c r="X3" s="35" t="inlineStr">
+      <c r="X3" s="36" t="inlineStr">
         <is>
           <t>Parkgebieden (P)</t>
         </is>
       </c>
-      <c r="Y3" s="35" t="inlineStr">
+      <c r="Y3" s="36" t="inlineStr">
         <is>
           <t>Buffe"rzones (T)</t>
         </is>
       </c>
-      <c r="Z3" s="36" t="inlineStr">
+      <c r="Z3" s="37" t="inlineStr">
         <is>
           <t>Landschappelijke waarevolle gebieden</t>
         </is>
       </c>
-      <c r="AA3" s="37" t="inlineStr">
+      <c r="AA3" s="38" t="inlineStr">
         <is>
           <t>Recreatiegebieden</t>
         </is>
       </c>
-      <c r="AB3" s="37" t="inlineStr">
+      <c r="AB3" s="38" t="inlineStr">
         <is>
           <t>Landelijke gebieen met toeristische waarde</t>
         </is>
       </c>
-      <c r="AC3" s="38" t="inlineStr">
+      <c r="AC3" s="39" t="inlineStr">
         <is>
           <t>Gebieden voor gemeenschapsvoorzieningen en openbare nutsvoorzieningen</t>
         </is>
       </c>
-      <c r="AD3" s="39" t="inlineStr">
+      <c r="AD3" s="40" t="inlineStr">
         <is>
           <t>Ontginningsgebieden</t>
         </is>
       </c>
-      <c r="AE3" s="101" t="inlineStr">
+      <c r="AE3" s="102" t="inlineStr">
         <is>
           <t>Gebieden voor dagrecreatie</t>
         </is>
       </c>
-      <c r="AF3" s="40" t="inlineStr">
+      <c r="AF3" s="41" t="inlineStr">
         <is>
           <t>Lien plan d'execution REGION</t>
         </is>
       </c>
-      <c r="AG3" s="40" t="inlineStr">
+      <c r="AG3" s="41" t="inlineStr">
         <is>
           <t>RUP</t>
         </is>
       </c>
-      <c r="AH3" s="25" t="inlineStr">
+      <c r="AH3" s="26" t="inlineStr">
         <is>
           <t>Wonen (zone d'habitat)</t>
         </is>
       </c>
-      <c r="AI3" s="25" t="inlineStr">
+      <c r="AI3" s="26" t="inlineStr">
         <is>
           <t>Zone voor kleinschalig wonen</t>
         </is>
       </c>
-      <c r="AJ3" s="41" t="inlineStr">
+      <c r="AJ3" s="42" t="inlineStr">
         <is>
           <t>Bedrijvigheid</t>
         </is>
       </c>
-      <c r="AK3" s="42" t="inlineStr">
+      <c r="AK3" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">Bedrijvigheid - Buffer
 </t>
         </is>
       </c>
-      <c r="AL3" s="37" t="inlineStr">
+      <c r="AL3" s="38" t="inlineStr">
         <is>
           <t>Recreatie</t>
         </is>
       </c>
-      <c r="AM3" s="37" t="inlineStr">
+      <c r="AM3" s="38" t="inlineStr">
         <is>
           <t>Recreatie (Natuurverwerving)</t>
         </is>
       </c>
-      <c r="AN3" s="33" t="inlineStr">
+      <c r="AN3" s="34" t="inlineStr">
         <is>
           <t>Landbouw- agrarisch gebied</t>
         </is>
       </c>
-      <c r="AO3" s="43" t="inlineStr">
+      <c r="AO3" s="44" t="inlineStr">
         <is>
           <t>Landbouw- agrarische bedrijvenzone</t>
         </is>
       </c>
-      <c r="AP3" s="44" t="inlineStr">
+      <c r="AP3" s="45" t="inlineStr">
         <is>
           <t>Landbouw- bouwvrij agrarisch gebied</t>
         </is>
       </c>
-      <c r="AQ3" s="44" t="inlineStr">
+      <c r="AQ3" s="45" t="inlineStr">
         <is>
           <t>Landbouw- Agrarisch gebied met ecologisch belang</t>
         </is>
       </c>
-      <c r="AR3" s="45" t="inlineStr">
+      <c r="AR3" s="46" t="inlineStr">
         <is>
           <t>Bois (Bos)</t>
         </is>
       </c>
-      <c r="AS3" s="46" t="inlineStr">
+      <c r="AS3" s="47" t="inlineStr">
         <is>
           <t>Zone verte (Overig groen - gemengd openruimtegebied)</t>
         </is>
       </c>
-      <c r="AT3" s="46" t="inlineStr">
+      <c r="AT3" s="47" t="inlineStr">
         <is>
           <t>Zone verte (Overig groen- parkgebied)</t>
         </is>
       </c>
-      <c r="AU3" s="46" t="inlineStr">
+      <c r="AU3" s="47" t="inlineStr">
         <is>
           <t>Zone verte - Overig groen-Gemengd openruimtegebied met cultuurhistorische waarde</t>
         </is>
       </c>
-      <c r="AV3" s="46" t="inlineStr">
+      <c r="AV3" s="47" t="inlineStr">
         <is>
           <t>Zone verte- Overig groen -bestaande, vergunde of vergund geachte weekendverblijven</t>
         </is>
       </c>
-      <c r="AW3" s="47" t="inlineStr">
+      <c r="AW3" s="48" t="inlineStr">
         <is>
           <t>Natuurgebied</t>
         </is>
       </c>
-      <c r="AX3" s="47" t="inlineStr">
+      <c r="AX3" s="48" t="inlineStr">
         <is>
           <t>Natuurreservaat</t>
         </is>
       </c>
-      <c r="AY3" s="48" t="inlineStr">
+      <c r="AY3" s="49" t="inlineStr">
         <is>
           <t>Gemeenschaps- en nutsvoorzieningen</t>
         </is>
       </c>
-      <c r="AZ3" s="48" t="inlineStr">
+      <c r="AZ3" s="49" t="inlineStr">
         <is>
           <t>Gebied voor zuiveringsinfrastructuur voor afvalwater</t>
         </is>
       </c>
-      <c r="BA3" s="48" t="inlineStr">
+      <c r="BA3" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">gebied voor infrastructuur voor duurzame watervoorziening </t>
         </is>
       </c>
-      <c r="BB3" s="48" t="inlineStr">
+      <c r="BB3" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">
 gebied voor de winning van oppervlaktedelfstoffen </t>
         </is>
       </c>
-      <c r="BC3" s="48" t="inlineStr">
+      <c r="BC3" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">gebied voor verwerking van oppervlaktedelfstoffen </t>
         </is>
       </c>
-      <c r="BD3" s="49" t="inlineStr">
+      <c r="BD3" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">Gebied voor projectgrindwinning
 </t>
         </is>
       </c>
-      <c r="BE3" s="40" t="inlineStr">
+      <c r="BE3" s="41" t="inlineStr">
         <is>
           <t>Lien plman d'execution PROVINCE</t>
         </is>
       </c>
-      <c r="BF3" s="40" t="inlineStr">
+      <c r="BF3" s="41" t="inlineStr">
         <is>
           <t>RUP</t>
         </is>
       </c>
-      <c r="BG3" s="25" t="inlineStr">
+      <c r="BG3" s="26" t="inlineStr">
         <is>
           <t>Wonen (zone d'habitat)</t>
         </is>
       </c>
-      <c r="BH3" s="25" t="inlineStr">
+      <c r="BH3" s="26" t="inlineStr">
         <is>
           <t>Zone voor kleinschalig wonen</t>
         </is>
       </c>
-      <c r="BI3" s="41" t="inlineStr">
+      <c r="BI3" s="42" t="inlineStr">
         <is>
           <t>Bedrijvigheid</t>
         </is>
       </c>
-      <c r="BJ3" s="41" t="inlineStr">
+      <c r="BJ3" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">Bedrijvigheid - Buffer
 </t>
         </is>
       </c>
-      <c r="BK3" s="37" t="inlineStr">
+      <c r="BK3" s="38" t="inlineStr">
         <is>
           <t>Recreatie</t>
         </is>
       </c>
-      <c r="BL3" s="37" t="inlineStr">
+      <c r="BL3" s="38" t="inlineStr">
         <is>
           <t>Recreatie (Natuurverwerving)</t>
         </is>
       </c>
-      <c r="BM3" s="33" t="inlineStr">
+      <c r="BM3" s="34" t="inlineStr">
         <is>
           <t>Landbouw- agrarisch gebied</t>
         </is>
       </c>
-      <c r="BN3" s="44" t="inlineStr">
+      <c r="BN3" s="45" t="inlineStr">
         <is>
           <t>Landbouw- agrarische bedrijvenzone</t>
         </is>
       </c>
-      <c r="BO3" s="44" t="inlineStr">
+      <c r="BO3" s="45" t="inlineStr">
         <is>
           <t>Landbouw- bouwvrij agrarisch gebied</t>
         </is>
       </c>
-      <c r="BP3" s="44" t="inlineStr">
+      <c r="BP3" s="45" t="inlineStr">
         <is>
           <t>Landbouw- Agrarisch gebied met ecologisch belang</t>
         </is>
       </c>
-      <c r="BQ3" s="45" t="inlineStr">
+      <c r="BQ3" s="46" t="inlineStr">
         <is>
           <t>Bois (Bos)</t>
         </is>
       </c>
-      <c r="BR3" s="46" t="inlineStr">
+      <c r="BR3" s="47" t="inlineStr">
         <is>
           <t>Zone verte (Overig groen - gemengd openruimtegebied)</t>
         </is>
       </c>
-      <c r="BS3" s="46" t="inlineStr">
+      <c r="BS3" s="47" t="inlineStr">
         <is>
           <t>Zone verte (Overig groen- parkgebied)</t>
         </is>
       </c>
-      <c r="BT3" s="46" t="inlineStr">
+      <c r="BT3" s="47" t="inlineStr">
         <is>
           <t>Zone verte - Overig groen-Gemengd openruimtegebied met cultuurhistorische waarde</t>
         </is>
       </c>
-      <c r="BU3" s="46" t="inlineStr">
+      <c r="BU3" s="47" t="inlineStr">
         <is>
           <t>Zone verte- Overig groen -bestaande, vergunde of vergund geachte weekendverblijven</t>
         </is>
       </c>
-      <c r="BV3" s="47" t="inlineStr">
+      <c r="BV3" s="48" t="inlineStr">
         <is>
           <t>Natuurgebied</t>
         </is>
       </c>
-      <c r="BW3" s="47" t="inlineStr">
+      <c r="BW3" s="48" t="inlineStr">
         <is>
           <t>Natuurreservaat</t>
         </is>
       </c>
-      <c r="BX3" s="48" t="inlineStr">
+      <c r="BX3" s="49" t="inlineStr">
         <is>
           <t>Gemeenschaps- en nutsvoorzieningen</t>
         </is>
       </c>
-      <c r="BY3" s="48" t="inlineStr">
+      <c r="BY3" s="49" t="inlineStr">
         <is>
           <t>Gebied voor zuiveringsinfrastructuur voor afvalwater</t>
         </is>
       </c>
-      <c r="BZ3" s="48" t="inlineStr">
+      <c r="BZ3" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">gebied voor infrastructuur voor duurzame watervoorziening </t>
         </is>
       </c>
-      <c r="CA3" s="48" t="inlineStr">
+      <c r="CA3" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">
 gebied voor de winning van oppervlaktedelfstoffen </t>
         </is>
       </c>
-      <c r="CB3" s="48" t="inlineStr">
+      <c r="CB3" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">gebied voor verwerking van oppervlaktedelfstoffen </t>
         </is>
       </c>
-      <c r="CC3" s="49" t="inlineStr">
+      <c r="CC3" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">Gebied voor projectgrindwinning
 </t>
         </is>
       </c>
-      <c r="CD3" s="40" t="inlineStr">
+      <c r="CD3" s="41" t="inlineStr">
         <is>
           <t>Lien  d'execution commune</t>
         </is>
       </c>
-      <c r="CE3" s="40" t="inlineStr">
+      <c r="CE3" s="41" t="inlineStr">
         <is>
           <t>RUP</t>
         </is>
       </c>
-      <c r="CF3" s="25" t="inlineStr">
+      <c r="CF3" s="26" t="inlineStr">
         <is>
           <t>Wonen (zone d'habitat)</t>
         </is>
       </c>
-      <c r="CG3" s="25" t="inlineStr">
+      <c r="CG3" s="26" t="inlineStr">
         <is>
           <t>Zone voor kleinschalig wonen</t>
         </is>
       </c>
-      <c r="CH3" s="41" t="inlineStr">
+      <c r="CH3" s="42" t="inlineStr">
         <is>
           <t>Bedrijvigheid</t>
         </is>
       </c>
-      <c r="CI3" s="50" t="inlineStr">
+      <c r="CI3" s="51" t="inlineStr">
         <is>
           <t xml:space="preserve">Bedrijvigheid - Buffer
 </t>
         </is>
       </c>
-      <c r="CJ3" s="37" t="inlineStr">
+      <c r="CJ3" s="38" t="inlineStr">
         <is>
           <t>Recreatie</t>
         </is>
       </c>
-      <c r="CK3" s="37" t="inlineStr">
+      <c r="CK3" s="38" t="inlineStr">
         <is>
           <t>Recreatie (Natuurverwerving)</t>
         </is>
       </c>
-      <c r="CL3" s="44" t="inlineStr">
+      <c r="CL3" s="45" t="inlineStr">
         <is>
           <t>Landbouw- agrarisch gebied</t>
         </is>
       </c>
-      <c r="CM3" s="44" t="inlineStr">
+      <c r="CM3" s="45" t="inlineStr">
         <is>
           <t>Landbouw- agrarische bedrijvenzone</t>
         </is>
       </c>
-      <c r="CN3" s="44" t="inlineStr">
+      <c r="CN3" s="45" t="inlineStr">
         <is>
           <t>Landbouw- bouwvrij agrarisch gebied</t>
         </is>
       </c>
-      <c r="CO3" s="44" t="inlineStr">
+      <c r="CO3" s="45" t="inlineStr">
         <is>
           <t>Landbouw- Agrarisch gebied met ecologisch belang</t>
         </is>
       </c>
-      <c r="CP3" s="45" t="inlineStr">
+      <c r="CP3" s="46" t="inlineStr">
         <is>
           <t>Bois (Bos)</t>
         </is>
       </c>
-      <c r="CQ3" s="46" t="inlineStr">
+      <c r="CQ3" s="47" t="inlineStr">
         <is>
           <t>Zone verte (Overig groen - gemengd openruimtegebied)</t>
         </is>
       </c>
-      <c r="CR3" s="46" t="inlineStr">
+      <c r="CR3" s="47" t="inlineStr">
         <is>
           <t>Zone verte (Overig groen- parkgebied)</t>
         </is>
       </c>
-      <c r="CS3" s="46" t="inlineStr">
+      <c r="CS3" s="47" t="inlineStr">
         <is>
           <t>Zone verte - Overig groen-Gemengd openruimtegebied met cultuurhistorische waarde</t>
         </is>
       </c>
-      <c r="CT3" s="46" t="inlineStr">
+      <c r="CT3" s="47" t="inlineStr">
         <is>
           <t>Zone verte- Overig groen -bestaande, vergunde of vergund geachte weekendverblijven</t>
         </is>
       </c>
-      <c r="CU3" s="47" t="inlineStr">
+      <c r="CU3" s="48" t="inlineStr">
         <is>
           <t>Natuurgebied</t>
         </is>
       </c>
-      <c r="CV3" s="47" t="inlineStr">
+      <c r="CV3" s="48" t="inlineStr">
         <is>
           <t>Natuurreservaat</t>
         </is>
       </c>
-      <c r="CW3" s="48" t="inlineStr">
+      <c r="CW3" s="49" t="inlineStr">
         <is>
           <t>Gemeenschaps- en nutsvoorzieningen</t>
         </is>
       </c>
-      <c r="CX3" s="48" t="inlineStr">
+      <c r="CX3" s="49" t="inlineStr">
         <is>
           <t>Gebied voor zuiveringsinfrastructuur voor afvalwater</t>
         </is>
       </c>
-      <c r="CY3" s="48" t="inlineStr">
+      <c r="CY3" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">gebied voor infrastructuur voor duurzame watervoorziening </t>
         </is>
       </c>
-      <c r="CZ3" s="51" t="inlineStr">
+      <c r="CZ3" s="52" t="inlineStr">
         <is>
           <t xml:space="preserve">
 gebied voor de winning van oppervlaktedelfstoffen </t>
         </is>
       </c>
-      <c r="DA3" s="48" t="inlineStr">
+      <c r="DA3" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">gebied voor verwerking van oppervlaktedelfstoffen </t>
         </is>
       </c>
-      <c r="DB3" s="49" t="inlineStr">
+      <c r="DB3" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">Gebied voor projectgrindwinning
 </t>
         </is>
       </c>
-      <c r="DC3" s="102" t="inlineStr">
+      <c r="DC3" s="103" t="inlineStr">
         <is>
           <t>Mogelijk overstromingsgevoelig</t>
         </is>
       </c>
-      <c r="DD3" s="52" t="inlineStr">
+      <c r="DD3" s="53" t="inlineStr">
         <is>
           <t>Effectief overstromingsgevoelig</t>
         </is>
       </c>
-      <c r="DE3" s="53" t="inlineStr">
+      <c r="DE3" s="54" t="inlineStr">
         <is>
           <t>Beheergebieden beheerovereenkomst waterwaliteit</t>
         </is>
       </c>
-      <c r="DF3" s="116" t="inlineStr">
+      <c r="DF3" s="121" t="inlineStr">
         <is>
           <t>Overstromingsgevoelige gebieden  Pluvial</t>
         </is>
       </c>
-      <c r="DG3" s="129" t="n"/>
-      <c r="DH3" s="129" t="n"/>
-      <c r="DI3" s="129" t="n"/>
-      <c r="DJ3" s="116" t="inlineStr">
+      <c r="DG3" s="137" t="n"/>
+      <c r="DH3" s="137" t="n"/>
+      <c r="DI3" s="137" t="n"/>
+      <c r="DJ3" s="121" t="inlineStr">
         <is>
           <t xml:space="preserve">Overstromingsgevoelige gebieden Fluvial </t>
         </is>
       </c>
-      <c r="DK3" s="129" t="n"/>
-      <c r="DL3" s="129" t="n"/>
-      <c r="DM3" s="129" t="n"/>
-      <c r="DN3" s="117" t="inlineStr">
+      <c r="DK3" s="137" t="n"/>
+      <c r="DL3" s="137" t="n"/>
+      <c r="DM3" s="137" t="n"/>
+      <c r="DN3" s="123" t="inlineStr">
         <is>
           <t>Overstromingsgevoelige gebieden vanuit zee</t>
         </is>
       </c>
-      <c r="DO3" s="129" t="n"/>
-      <c r="DP3" s="129" t="n"/>
-      <c r="DQ3" s="130" t="n"/>
-      <c r="DR3" s="114" t="inlineStr">
+      <c r="DO3" s="137" t="n"/>
+      <c r="DP3" s="137" t="n"/>
+      <c r="DQ3" s="138" t="n"/>
+      <c r="DR3" s="139" t="inlineStr">
         <is>
           <t>Afgebakende overstromingsgebieden en oeverzones</t>
         </is>
       </c>
-      <c r="DS3" s="129" t="n"/>
-      <c r="DT3" s="114" t="inlineStr">
+      <c r="DS3" s="138" t="n"/>
+      <c r="DT3" s="139" t="inlineStr">
         <is>
           <t>Signaalgebieden</t>
         </is>
       </c>
-      <c r="DU3" s="129" t="n"/>
-      <c r="DV3" s="54" t="inlineStr">
+      <c r="DU3" s="138" t="n"/>
+      <c r="DV3" s="55" t="inlineStr">
         <is>
           <t>Grond waterstromingsgevoelige gebieden</t>
         </is>
       </c>
-      <c r="DW3" s="55" t="inlineStr">
+      <c r="DW3" s="56" t="inlineStr">
         <is>
           <t>Van Natuur overstroombare gebieden</t>
         </is>
       </c>
-      <c r="DX3" s="56" t="inlineStr">
+      <c r="DX3" s="57" t="inlineStr">
         <is>
           <t>Risicozones voor overstromingen: nieuwe en bevestigde risocozones</t>
         </is>
       </c>
-      <c r="DY3" s="57" t="inlineStr">
+      <c r="DY3" s="58" t="inlineStr">
         <is>
           <t>Recent overstromde gebieden</t>
         </is>
       </c>
-      <c r="DZ3" s="58" t="inlineStr">
+      <c r="DZ3" s="59" t="inlineStr">
         <is>
           <t>Overstromingsgebieden en oeverzones - integraal waterbeleid</t>
         </is>
       </c>
-      <c r="EA3" s="59" t="inlineStr">
+      <c r="EA3" s="60" t="inlineStr">
         <is>
           <t>Grondwaterwingebieden en beschermingszones</t>
         </is>
       </c>
-      <c r="EB3" s="60" t="inlineStr">
+      <c r="EB3" s="61" t="inlineStr">
         <is>
           <t>Infiltratiegevoelige bodems</t>
         </is>
       </c>
-      <c r="EC3" s="58" t="inlineStr">
+      <c r="EC3" s="59" t="inlineStr">
         <is>
           <t>Afstromingskaart (enkelvoudige stroomlijnen)</t>
         </is>
       </c>
-      <c r="ED3" s="58" t="n"/>
-      <c r="EE3" s="58" t="n"/>
-      <c r="EF3" s="58" t="n"/>
-      <c r="EG3" s="58" t="n"/>
-      <c r="EH3" s="58" t="n"/>
-      <c r="EI3" s="103" t="inlineStr">
+      <c r="ED3" s="59" t="n"/>
+      <c r="EE3" s="59" t="n"/>
+      <c r="EF3" s="59" t="n"/>
+      <c r="EG3" s="59" t="n"/>
+      <c r="EH3" s="59" t="n"/>
+      <c r="EI3" s="104" t="inlineStr">
         <is>
           <t>Andere erosiegerelateerde gronden</t>
         </is>
       </c>
-      <c r="EJ3" s="56" t="inlineStr">
+      <c r="EJ3" s="57" t="inlineStr">
         <is>
           <t>Gekarteerde grondverschuivingen</t>
         </is>
       </c>
-      <c r="EK3" s="61" t="inlineStr">
+      <c r="EK3" s="62" t="inlineStr">
         <is>
           <t>Gevoeligheid voor grondverschuivingen</t>
         </is>
       </c>
-      <c r="EL3" s="62" t="inlineStr">
+      <c r="EL3" s="63" t="inlineStr">
         <is>
           <t>Potentiële bodemerosiekaart per perceel 2021</t>
         </is>
       </c>
-      <c r="EM3" s="63" t="inlineStr">
+      <c r="EM3" s="64" t="inlineStr">
         <is>
           <t>Watertoets</t>
         </is>
       </c>
-      <c r="EN3" s="64" t="inlineStr">
+      <c r="EN3" s="65" t="inlineStr">
         <is>
           <t>Aangeboden bedrijventerreinperceel</t>
         </is>
       </c>
-      <c r="EO3" s="59" t="inlineStr">
+      <c r="EO3" s="60" t="inlineStr">
         <is>
           <t>Bedrijventerrein</t>
         </is>
       </c>
-      <c r="EP3" s="59" t="inlineStr">
+      <c r="EP3" s="60" t="inlineStr">
         <is>
           <t>Beheerde bedrijvenzone</t>
         </is>
       </c>
-      <c r="EQ3" s="65" t="inlineStr">
+      <c r="EQ3" s="66" t="inlineStr">
         <is>
           <t>Ontwikkelbare bedrijvenzone</t>
         </is>
@@ -2640,99 +2758,99 @@
           <t>Planningszone met economische bestemming</t>
         </is>
       </c>
-      <c r="ES3" s="66" t="inlineStr">
+      <c r="ES3" s="67" t="inlineStr">
         <is>
           <t>Brownfieldconvenanten</t>
         </is>
       </c>
-      <c r="ET3" s="59" t="inlineStr">
+      <c r="ET3" s="60" t="inlineStr">
         <is>
           <t>Steunzone</t>
         </is>
       </c>
-      <c r="EU3" s="67" t="inlineStr">
+      <c r="EU3" s="68" t="inlineStr">
         <is>
           <t>Seveso inrichingen</t>
         </is>
       </c>
-      <c r="EV3" s="68" t="inlineStr">
+      <c r="EV3" s="69" t="inlineStr">
         <is>
           <t>Consultatie zone van Seveso-inrichtingen</t>
         </is>
       </c>
-      <c r="EW3" s="43" t="inlineStr">
+      <c r="EW3" s="44" t="inlineStr">
         <is>
           <t>Landinrichting in onderzoek</t>
         </is>
       </c>
-      <c r="EX3" s="69" t="inlineStr">
+      <c r="EX3" s="70" t="inlineStr">
         <is>
           <t>Vastgesteld landinrichtingsproject</t>
         </is>
       </c>
-      <c r="EY3" s="70" t="inlineStr">
+      <c r="EY3" s="71" t="inlineStr">
         <is>
           <t>Landinrichtingsplan</t>
         </is>
       </c>
-      <c r="EZ3" s="35" t="inlineStr">
+      <c r="EZ3" s="36" t="inlineStr">
         <is>
           <t>Natuurinrichting</t>
         </is>
       </c>
-      <c r="FA3" s="25" t="inlineStr">
+      <c r="FA3" s="26" t="inlineStr">
         <is>
           <t>Ruilverkaveling
 (Ruilverkaveling van landeigendommen uit kracht van wet)</t>
         </is>
       </c>
-      <c r="FB3" s="71" t="inlineStr">
+      <c r="FB3" s="72" t="inlineStr">
         <is>
           <t>Fysische systeemeenheden</t>
         </is>
       </c>
-      <c r="FC3" s="72" t="inlineStr">
+      <c r="FC3" s="73" t="inlineStr">
         <is>
           <t>Traditionele landschappen</t>
         </is>
       </c>
-      <c r="FD3" s="61" t="inlineStr">
+      <c r="FD3" s="62" t="inlineStr">
         <is>
           <t>Beheergebieden Natura 2000-soorten</t>
         </is>
       </c>
-      <c r="FE3" s="73" t="inlineStr">
+      <c r="FE3" s="74" t="inlineStr">
         <is>
           <t>Bosreservaten</t>
         </is>
       </c>
-      <c r="FF3" s="65" t="inlineStr">
+      <c r="FF3" s="66" t="inlineStr">
         <is>
           <t>Erkende Natuurreservaten</t>
         </is>
       </c>
-      <c r="FG3" s="61" t="inlineStr">
+      <c r="FG3" s="62" t="inlineStr">
         <is>
           <t>Gebieden duinendecreet</t>
         </is>
       </c>
-      <c r="FH3" s="74" t="inlineStr">
+      <c r="FH3" s="75" t="inlineStr">
         <is>
           <t>Gebieden van het VEN en het IVON
 (VEN en het IVON)</t>
         </is>
       </c>
-      <c r="FI3" s="75" t="inlineStr">
+      <c r="FI3" s="76" t="inlineStr">
         <is>
           <t>Habitatrichtlijngebieden</t>
         </is>
       </c>
-      <c r="FJ3" s="76" t="inlineStr">
+      <c r="FJ3" s="77" t="inlineStr">
         <is>
           <t>Vogelrichtlijngebieden</t>
         </is>
       </c>
-      <c r="FK3" s="20" t="inlineStr">
+      <c r="FK3" s="21" t="inlineStr">
         <is>
           <t>Geluidsbelasting belangrijke wegen Lnight 2021
   (Exposition au bruit- routes)</t>
@@ -2742,7 +2860,7 @@
       <c r="FM3" s="1" t="n"/>
       <c r="FN3" s="1" t="n"/>
       <c r="FO3" s="1" t="n"/>
-      <c r="FP3" s="20" t="inlineStr">
+      <c r="FP3" s="21" t="inlineStr">
         <is>
           <t>Geluidsbelasting belangrijke luchthaven(s) Lnight 2021(Exposition au bruit- voies ferrées)</t>
         </is>
@@ -2751,7 +2869,7 @@
       <c r="FR3" s="1" t="n"/>
       <c r="FS3" s="1" t="n"/>
       <c r="FT3" s="1" t="n"/>
-      <c r="FU3" s="20" t="inlineStr">
+      <c r="FU3" s="21" t="inlineStr">
         <is>
           <t>Geluidsbelasting Geluidsbelasting belangrijke spoorwegen Lden 2021 (Exposition au bruit- aéroport)</t>
         </is>
@@ -2760,32 +2878,32 @@
       <c r="FW3" s="1" t="n"/>
       <c r="FX3" s="1" t="n"/>
       <c r="FY3" s="1" t="n"/>
-      <c r="FZ3" s="82" t="inlineStr">
+      <c r="FZ3" s="83" t="inlineStr">
         <is>
           <t>Bodem is licht verontreinigd</t>
         </is>
       </c>
-      <c r="GA3" s="83" t="inlineStr">
+      <c r="GA3" s="84" t="inlineStr">
         <is>
           <t>Bodem is proper</t>
         </is>
       </c>
-      <c r="GB3" s="84" t="inlineStr">
+      <c r="GB3" s="85" t="inlineStr">
         <is>
           <t>Bodem is verontreinigd</t>
         </is>
       </c>
-      <c r="GC3" s="85" t="inlineStr">
+      <c r="GC3" s="86" t="inlineStr">
         <is>
           <t>Bodeminfo wordt gecheckt</t>
         </is>
       </c>
-      <c r="GD3" s="79" t="inlineStr">
+      <c r="GD3" s="80" t="inlineStr">
         <is>
           <t>Mogelijke risicogrond</t>
         </is>
       </c>
-      <c r="GE3" s="80" t="inlineStr">
+      <c r="GE3" s="81" t="inlineStr">
         <is>
           <t>Geen bodeminfo</t>
         </is>
@@ -2795,942 +2913,942 @@
           <t>Woningbouwgebieden</t>
         </is>
       </c>
-      <c r="GG3" s="77" t="inlineStr">
+      <c r="GG3" s="78" t="inlineStr">
         <is>
           <t>Woonvernieuwingsgebieden</t>
         </is>
       </c>
     </row>
     <row r="4" ht="23.25" customHeight="1">
-      <c r="A4" s="86" t="n"/>
-      <c r="B4" s="86" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="C4" s="86" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="D4" s="87" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="E4" s="87" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F4" s="111" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="G4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="H4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="I4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="J4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="K4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="L4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="M4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="N4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="O4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="P4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="Q4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="R4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="S4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="T4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="U4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="V4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="W4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="X4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="Y4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="Z4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AA4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AB4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AC4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AD4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AE4" s="88" t="n"/>
-      <c r="AF4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AH4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AI4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AJ4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AK4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AL4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AM4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AN4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AO4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AP4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AQ4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AR4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AS4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AT4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AU4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AV4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AW4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AX4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AY4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AZ4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BA4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BB4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BC4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BD4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BE4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BF4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BG4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BH4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BI4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BJ4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BK4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BL4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BM4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BN4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BO4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BP4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BQ4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BR4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BS4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BT4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BU4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BV4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BW4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BX4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BY4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="BZ4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CA4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CB4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CC4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CD4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CE4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CF4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CG4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CH4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CI4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CJ4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CK4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CL4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CM4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CN4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CO4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CP4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CQ4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CR4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CS4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CT4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CU4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CV4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CW4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CX4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CY4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="CZ4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="DA4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="DB4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="DC4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="DD4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="DE4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="DF4" s="104" t="inlineStr">
+      <c r="A4" s="87" t="n"/>
+      <c r="B4" s="87" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="C4" s="87" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="D4" s="88" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="E4" s="88" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F4" s="112" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="G4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="I4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="J4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="K4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="L4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="M4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="N4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="O4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="P4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="Q4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="R4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="S4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="T4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="U4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="V4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="W4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="X4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="Y4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="Z4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AA4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AB4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AC4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AD4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AE4" s="89" t="n"/>
+      <c r="AF4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AH4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AI4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AJ4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AK4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AL4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AM4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AN4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AO4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AP4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AQ4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AR4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AS4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AT4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AU4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AV4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AW4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AX4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AY4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AZ4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BA4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BB4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BC4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BD4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BE4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BF4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BG4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BH4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BI4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BJ4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BK4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BL4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BM4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BN4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BO4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BP4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BQ4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BR4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BS4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BT4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BU4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BV4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BW4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BX4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BY4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BZ4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CA4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CB4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CC4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CD4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CE4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CF4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CG4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CH4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CI4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CJ4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CK4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CL4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CM4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CN4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CO4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CP4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CQ4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CR4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CS4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CT4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CU4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CV4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CW4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CX4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CY4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CZ4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="DA4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="DB4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="DC4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="DD4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="DE4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="DF4" s="105" t="inlineStr">
         <is>
           <t>Geen overstroming gemodelleerd</t>
         </is>
       </c>
-      <c r="DG4" s="105" t="inlineStr">
+      <c r="DG4" s="106" t="inlineStr">
         <is>
           <t>Kleine kans op overstromingen onder klimaatverandering</t>
         </is>
       </c>
-      <c r="DH4" s="106" t="inlineStr">
+      <c r="DH4" s="107" t="inlineStr">
         <is>
           <t>Kleine kans op overstromingen</t>
         </is>
       </c>
-      <c r="DI4" s="107" t="inlineStr">
+      <c r="DI4" s="108" t="inlineStr">
         <is>
           <t>Middelgrote kans op overstromingen</t>
         </is>
       </c>
-      <c r="DJ4" s="104" t="inlineStr">
+      <c r="DJ4" s="105" t="inlineStr">
         <is>
           <t>Geen overstroming gemodelleerd</t>
         </is>
       </c>
-      <c r="DK4" s="105" t="inlineStr">
+      <c r="DK4" s="106" t="inlineStr">
         <is>
           <t>Kleine kans op overstromingen onder klimaatverandering</t>
         </is>
       </c>
-      <c r="DL4" s="106" t="inlineStr">
+      <c r="DL4" s="107" t="inlineStr">
         <is>
           <t>Kleine kans op overstromingen</t>
         </is>
       </c>
-      <c r="DM4" s="107" t="inlineStr">
+      <c r="DM4" s="108" t="inlineStr">
         <is>
           <t>Middelgrote kans op overstromingen</t>
         </is>
       </c>
-      <c r="DN4" s="104" t="inlineStr">
+      <c r="DN4" s="105" t="inlineStr">
         <is>
           <t>Geen overstroming gemodelleerd</t>
         </is>
       </c>
-      <c r="DO4" s="105" t="inlineStr">
+      <c r="DO4" s="106" t="inlineStr">
         <is>
           <t>Kleine kans op overstromingen onder klimaatverandering</t>
         </is>
       </c>
-      <c r="DP4" s="106" t="inlineStr">
+      <c r="DP4" s="107" t="inlineStr">
         <is>
           <t>Kleine kans op overstromingen</t>
         </is>
       </c>
-      <c r="DQ4" s="107" t="inlineStr">
+      <c r="DQ4" s="108" t="inlineStr">
         <is>
           <t>Middelgrote kans op overstromingen</t>
         </is>
       </c>
-      <c r="DR4" s="108" t="inlineStr">
+      <c r="DR4" s="109" t="inlineStr">
         <is>
           <t>IWB OeverzoneI</t>
         </is>
       </c>
-      <c r="DS4" s="108" t="inlineStr">
+      <c r="DS4" s="109" t="inlineStr">
         <is>
           <t>WB Overstromingsgebied</t>
         </is>
       </c>
-      <c r="DT4" s="109" t="inlineStr">
+      <c r="DT4" s="110" t="inlineStr">
         <is>
           <t>Bouwvrije opgave</t>
         </is>
       </c>
-      <c r="DU4" s="110" t="inlineStr">
+      <c r="DU4" s="111" t="inlineStr">
         <is>
           <t>Verscherpte watertoets</t>
         </is>
       </c>
-      <c r="DV4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="DW4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="DX4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="DY4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="DZ4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="EA4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="EB4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="EC4" s="89" t="inlineStr">
+      <c r="DV4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="DW4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="DX4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="DY4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="DZ4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="EA4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="EB4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="EC4" s="90" t="inlineStr">
         <is>
           <t>0,5-5 ha</t>
         </is>
       </c>
-      <c r="ED4" s="90" t="inlineStr">
+      <c r="ED4" s="91" t="inlineStr">
         <is>
           <t>5-10 ha</t>
         </is>
       </c>
-      <c r="EE4" s="91" t="inlineStr">
+      <c r="EE4" s="92" t="inlineStr">
         <is>
           <t>10-20ha</t>
         </is>
       </c>
-      <c r="EF4" s="92" t="inlineStr">
+      <c r="EF4" s="93" t="inlineStr">
         <is>
           <t>20-50 ha</t>
         </is>
       </c>
-      <c r="EG4" s="93" t="inlineStr">
+      <c r="EG4" s="94" t="inlineStr">
         <is>
           <t>50-100 ha</t>
         </is>
       </c>
-      <c r="EH4" s="94" t="inlineStr">
+      <c r="EH4" s="95" t="inlineStr">
         <is>
           <t>&gt;100 ha</t>
         </is>
       </c>
-      <c r="EI4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="EJ4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="EK4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="EL4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="EM4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="EN4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="EO4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="EP4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="EQ4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="ER4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="ES4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="ET4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="EU4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="EV4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="EW4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="EX4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="EY4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="EZ4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="FA4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="FB4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="FC4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="FD4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="FE4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="FF4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="FG4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="FH4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="FI4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="FJ4" s="88" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="FK4" s="95" t="inlineStr">
+      <c r="EI4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="EJ4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="EK4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="EL4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="EM4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="EN4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="EO4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="EP4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="EQ4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="ER4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="ES4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="ET4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="EU4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="EV4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="EW4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="EX4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="EY4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="EZ4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="FA4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="FB4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="FC4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="FD4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="FE4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="FF4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="FG4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="FH4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="FI4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="FJ4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="FK4" s="96" t="inlineStr">
         <is>
           <t>50-55 dB (décibel)</t>
         </is>
       </c>
-      <c r="FL4" s="96" t="inlineStr">
+      <c r="FL4" s="97" t="inlineStr">
         <is>
           <t>55-60 dB</t>
         </is>
       </c>
-      <c r="FM4" s="97" t="inlineStr">
+      <c r="FM4" s="98" t="inlineStr">
         <is>
           <t>60-65 dB</t>
         </is>
       </c>
-      <c r="FN4" s="98" t="inlineStr">
+      <c r="FN4" s="99" t="inlineStr">
         <is>
           <t>65-70 dB</t>
         </is>
       </c>
-      <c r="FO4" s="99" t="inlineStr">
+      <c r="FO4" s="100" t="inlineStr">
         <is>
           <t>&gt; 70 dB</t>
         </is>
       </c>
-      <c r="FP4" s="95" t="inlineStr">
+      <c r="FP4" s="96" t="inlineStr">
         <is>
           <t>50-55 dB (décibel)</t>
         </is>
       </c>
-      <c r="FQ4" s="96" t="inlineStr">
+      <c r="FQ4" s="97" t="inlineStr">
         <is>
           <t>55-60 dB</t>
         </is>
       </c>
-      <c r="FR4" s="97" t="inlineStr">
+      <c r="FR4" s="98" t="inlineStr">
         <is>
           <t>60-65 dB</t>
         </is>
       </c>
-      <c r="FS4" s="98" t="inlineStr">
+      <c r="FS4" s="99" t="inlineStr">
         <is>
           <t>65-70 dB</t>
         </is>
       </c>
-      <c r="FT4" s="99" t="inlineStr">
+      <c r="FT4" s="100" t="inlineStr">
         <is>
           <t>&gt; 70 dB</t>
         </is>
       </c>
-      <c r="FU4" s="95" t="inlineStr">
+      <c r="FU4" s="96" t="inlineStr">
         <is>
           <t>50-55 dB (décibel)</t>
         </is>
       </c>
-      <c r="FV4" s="96" t="inlineStr">
+      <c r="FV4" s="97" t="inlineStr">
         <is>
           <t>55-60 dB</t>
         </is>
       </c>
-      <c r="FW4" s="97" t="inlineStr">
+      <c r="FW4" s="98" t="inlineStr">
         <is>
           <t>60-65 dB</t>
         </is>
       </c>
-      <c r="FX4" s="98" t="inlineStr">
+      <c r="FX4" s="99" t="inlineStr">
         <is>
           <t>65-70 dB</t>
         </is>
       </c>
-      <c r="FY4" s="99" t="inlineStr">
+      <c r="FY4" s="100" t="inlineStr">
         <is>
           <t>&gt; 70 dB</t>
         </is>
       </c>
-      <c r="FZ4" s="100" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="GA4" s="100" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="GB4" s="100" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="GC4" s="100" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="GF4" s="100" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="GG4" s="100" t="inlineStr">
+      <c r="FZ4" s="101" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="GA4" s="101" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="GB4" s="101" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="GC4" s="101" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="GF4" s="101" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="GG4" s="101" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
     </row>
-    <row r="5" customFormat="1" s="120">
+    <row r="5">
       <c r="A5" t="inlineStr">
         <is>
           <t>Sint-Truiden</t>
@@ -3761,6 +3879,381 @@
           <t>O</t>
         </is>
       </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CJ5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CK5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CL5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CM5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CN5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CO5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CP5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CS5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CT5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CU5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CV5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CW5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CX5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CY5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CZ5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="DA5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="DB5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="DF5" t="inlineStr">
         <is>
           <t>O</t>
@@ -3927,7 +4420,7 @@
         </is>
       </c>
     </row>
-    <row r="6" customFormat="1" s="120">
+    <row r="6">
       <c r="A6" t="inlineStr">
         <is>
           <t>Sint-Truiden</t>
@@ -3958,6 +4451,381 @@
           <t>O</t>
         </is>
       </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CJ6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CK6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CL6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CM6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CN6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CO6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CP6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CS6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CT6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CU6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CV6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CW6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CX6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CY6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CZ6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="DA6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="DB6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="DF6" t="inlineStr">
         <is>
           <t>O</t>
@@ -4124,7 +4992,7 @@
         </is>
       </c>
     </row>
-    <row r="7" customFormat="1" s="120">
+    <row r="7">
       <c r="A7" t="inlineStr">
         <is>
           <t>Sint-Truiden</t>
@@ -4155,6 +5023,381 @@
           <t>O</t>
         </is>
       </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CI7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CJ7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CK7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CL7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CM7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CN7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CO7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CP7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CS7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CT7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CU7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CV7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CW7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CX7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CY7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CZ7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="DA7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="DB7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="DF7" t="inlineStr">
         <is>
           <t>O</t>
@@ -4321,7 +5564,7 @@
         </is>
       </c>
     </row>
-    <row r="8" customFormat="1" s="120">
+    <row r="8">
       <c r="A8" t="inlineStr">
         <is>
           <t>Sint-Truiden</t>
@@ -4352,6 +5595,381 @@
           <t>O</t>
         </is>
       </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CJ8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CK8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CL8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CM8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CN8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CO8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CP8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CS8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CT8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CU8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CV8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CW8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CX8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CY8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CZ8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="DA8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="DB8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="DF8" t="inlineStr">
         <is>
           <t>O</t>
@@ -4518,7 +6136,7 @@
         </is>
       </c>
     </row>
-    <row r="9" customFormat="1" s="120">
+    <row r="9">
       <c r="A9" t="inlineStr">
         <is>
           <t>Sint-Truiden</t>
@@ -4549,6 +6167,381 @@
           <t>O</t>
         </is>
       </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CI9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CJ9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CK9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CL9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CM9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CN9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CO9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CP9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CS9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CT9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CU9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CV9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CW9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CX9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CY9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CZ9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="DA9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="DB9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="DF9" t="inlineStr">
         <is>
           <t>O</t>
@@ -4715,7 +6708,7 @@
         </is>
       </c>
     </row>
-    <row r="10" customFormat="1" s="120">
+    <row r="10">
       <c r="A10" t="inlineStr">
         <is>
           <t>Sint-Truiden</t>
@@ -4746,6 +6739,381 @@
           <t>O</t>
         </is>
       </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CJ10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CK10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CL10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CM10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CN10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CO10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CP10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CS10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CT10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CU10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CV10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CW10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CX10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CY10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CZ10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="DA10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="DB10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="DF10" t="inlineStr">
         <is>
           <t>O</t>
@@ -4912,7 +7280,7 @@
         </is>
       </c>
     </row>
-    <row r="11" customFormat="1" s="120">
+    <row r="11">
       <c r="A11" t="inlineStr">
         <is>
           <t>Sint-Truiden</t>
@@ -4943,6 +7311,381 @@
           <t>O</t>
         </is>
       </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CI11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CJ11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CK11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CL11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CM11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CN11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CO11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CP11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CQ11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CS11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CT11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CU11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CV11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CW11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CX11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CY11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="CZ11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="DA11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="DB11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="DF11" t="inlineStr">
         <is>
           <t>O</t>
@@ -5109,14 +7852,6 @@
         </is>
       </c>
     </row>
-    <row r="12" customFormat="1" s="120"/>
-    <row r="13" customFormat="1" s="120"/>
-    <row r="14" customFormat="1" s="120"/>
-    <row r="15" customFormat="1" s="120"/>
-    <row r="16" customFormat="1" s="120"/>
-    <row r="17" customFormat="1" s="120"/>
-    <row r="18" customFormat="1" s="120"/>
-    <row r="19" customFormat="1" s="125"/>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="DN3:DQ3"/>
@@ -5128,4 +7863,377 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N11"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <cols>
+    <col width="35.28515625" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="165" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Commune</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>Code postal</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>Rue</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>Numéro</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>Numéro cadastral</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>Plans d'exécution spatiaux (Région) (Ruimtelijke uitvoeringsplannen RUP- Gewest)</t>
+        </is>
+      </c>
+      <c r="G2" s="11" t="inlineStr">
+        <is>
+          <t>Chercher commune par commune https://dsi.omgeving.vlaanderen.be/fiche-overzicht?locatie=41002 + indiquer le lien vers le RUP</t>
+        </is>
+      </c>
+      <c r="H2" s="11" t="n"/>
+      <c r="I2" s="9" t="inlineStr">
+        <is>
+          <t>Plans d'exécution spatiaux (Province) (Ruimtelijke uitvoeringsplannen RUP- Provincie)</t>
+        </is>
+      </c>
+      <c r="J2" s="11" t="inlineStr">
+        <is>
+          <t>Chercher commune par commune https://dsi.omgeving.vlaanderen.be/fiche-overzicht?locatie=41002 + indiquer le lien vers le RUP</t>
+        </is>
+      </c>
+      <c r="K2" s="11" t="n"/>
+      <c r="L2" s="9" t="inlineStr">
+        <is>
+          <t>Plans d'exécution spatiaux (Commune) (Ruimtelijke uitvoeringsplannen RUP- Gemeente)</t>
+        </is>
+      </c>
+      <c r="M2" s="11" t="inlineStr">
+        <is>
+          <t>Chercher commune par commune https://dsi.omgeving.vlaanderen.be/fiche-overzicht?locatie=41002 + indiquer le lien vers le RUP</t>
+        </is>
+      </c>
+      <c r="N2" s="11" t="n"/>
+    </row>
+    <row r="3" ht="33.75" customHeight="1">
+      <c r="A3" s="23" t="n"/>
+      <c r="B3" s="23" t="n"/>
+      <c r="C3" s="24" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="41" t="inlineStr">
+        <is>
+          <t>Lien plan d'execution REGION</t>
+        </is>
+      </c>
+      <c r="G3" s="41" t="inlineStr">
+        <is>
+          <t>RUP</t>
+        </is>
+      </c>
+      <c r="H3" s="115" t="n"/>
+      <c r="I3" s="41" t="inlineStr">
+        <is>
+          <t>Lien plman d'execution PROVINCE</t>
+        </is>
+      </c>
+      <c r="J3" s="41" t="inlineStr">
+        <is>
+          <t>RUP</t>
+        </is>
+      </c>
+      <c r="K3" s="115" t="n"/>
+      <c r="L3" s="41" t="inlineStr">
+        <is>
+          <t>Lien  d'execution commune</t>
+        </is>
+      </c>
+      <c r="M3" s="41" t="inlineStr">
+        <is>
+          <t>RUP</t>
+        </is>
+      </c>
+      <c r="N3" s="115" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="87" t="n"/>
+      <c r="B4" s="87" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="C4" s="87" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="D4" s="88" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="E4" s="88" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="G4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H4" s="89" t="n"/>
+      <c r="I4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="J4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="K4" s="89" t="n"/>
+      <c r="L4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="M4" s="89" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="N4" s="89" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sint-Truiden</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>3800</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Heilig-Hartplein</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>71053H1081/00_000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sint-Truiden</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>3800</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Heilig-Hartplein</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>71053H1049/00B000</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sint-Truiden</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>3800</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Heilig-Hartplein</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>71053H1051/00N000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sint-Truiden</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>3800</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Heilig-Hartplein</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>7B</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>71053H1303/00A000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sint-Truiden</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>3800</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Heilig-Hartplein</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>71053H1059/00K000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sint-Truiden</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>3800</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Heilig-Hartplein</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>71053H1050/00E000</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sint-Truiden</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>3800</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Heilig-Hartplein</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>71053H1058/00D000</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/state/3800_sint-truiden.xlsx
+++ b/state/3800_sint-truiden.xlsx
@@ -8070,6 +8070,26 @@
           <t>71053H1081/00_000</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>https://dsi.omgeving.vlaanderen.be/fiche-detail/bf6f470b-8bfe-4ef7-9586-307ecb34a2ab</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>KSG Sint-Truiden — Afbakeningslijn structuurondersteunend  kleinstedelijk gebied Sint-Truiden</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://dsi.omgeving.vlaanderen.be/fiche-detail/4d0b4cca-0fb4-42b3-b172-c1e6f3b93d03</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Binnenstad — kernwinkelgebied; straten en pleinen</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8097,6 +8117,26 @@
           <t>71053H1049/00B000</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>https://dsi.omgeving.vlaanderen.be/fiche-detail/bf6f470b-8bfe-4ef7-9586-307ecb34a2ab</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>KSG Sint-Truiden — Afbakeningslijn structuurondersteunend  kleinstedelijk gebied Sint-Truiden</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://dsi.omgeving.vlaanderen.be/fiche-detail/4d0b4cca-0fb4-42b3-b172-c1e6f3b93d03</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Binnenstad — kernwinkelgebied; straten en pleinen</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8124,6 +8164,26 @@
           <t>71053H1051/00N000</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>https://dsi.omgeving.vlaanderen.be/fiche-detail/bf6f470b-8bfe-4ef7-9586-307ecb34a2ab</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>KSG Sint-Truiden — Afbakeningslijn structuurondersteunend  kleinstedelijk gebied Sint-Truiden</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://dsi.omgeving.vlaanderen.be/fiche-detail/4d0b4cca-0fb4-42b3-b172-c1e6f3b93d03</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Binnenstad — horecaprojectzone; kernwinkelgebied</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8151,6 +8211,26 @@
           <t>71053H1303/00A000</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>https://dsi.omgeving.vlaanderen.be/fiche-detail/bf6f470b-8bfe-4ef7-9586-307ecb34a2ab</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>KSG Sint-Truiden — Afbakeningslijn structuurondersteunend  kleinstedelijk gebied Sint-Truiden</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://dsi.omgeving.vlaanderen.be/fiche-detail/4d0b4cca-0fb4-42b3-b172-c1e6f3b93d03</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Binnenstad — horecaprojectzone; woonzone met tuinstrook</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8178,6 +8258,26 @@
           <t>71053H1059/00K000</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>https://dsi.omgeving.vlaanderen.be/fiche-detail/bf6f470b-8bfe-4ef7-9586-307ecb34a2ab</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>KSG Sint-Truiden — Afbakeningslijn structuurondersteunend  kleinstedelijk gebied Sint-Truiden</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://dsi.omgeving.vlaanderen.be/fiche-detail/4d0b4cca-0fb4-42b3-b172-c1e6f3b93d03</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Binnenstad — woonzone met tuinstrook</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8205,6 +8305,26 @@
           <t>71053H1050/00E000</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>https://dsi.omgeving.vlaanderen.be/fiche-detail/bf6f470b-8bfe-4ef7-9586-307ecb34a2ab</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>KSG Sint-Truiden — Afbakeningslijn structuurondersteunend  kleinstedelijk gebied Sint-Truiden</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://dsi.omgeving.vlaanderen.be/fiche-detail/4d0b4cca-0fb4-42b3-b172-c1e6f3b93d03</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Binnenstad — horecaprojectzone; kernwinkelgebied</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8230,6 +8350,26 @@
       <c r="E11" t="inlineStr">
         <is>
           <t>71053H1058/00D000</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>https://dsi.omgeving.vlaanderen.be/fiche-detail/bf6f470b-8bfe-4ef7-9586-307ecb34a2ab</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>KSG Sint-Truiden — Afbakeningslijn structuurondersteunend  kleinstedelijk gebied Sint-Truiden</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://dsi.omgeving.vlaanderen.be/fiche-detail/4d0b4cca-0fb4-42b3-b172-c1e6f3b93d03</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Binnenstad — woonzone met tuinstrook</t>
         </is>
       </c>
     </row>

--- a/state/3800_sint-truiden.xlsx
+++ b/state/3800_sint-truiden.xlsx
@@ -4274,6 +4274,11 @@
           <t>O</t>
         </is>
       </c>
+      <c r="DY5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="EA5" t="inlineStr">
         <is>
           <t>N</t>
@@ -4369,6 +4374,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="FA5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="FB5" t="inlineStr">
         <is>
           <t>N</t>
@@ -4377,6 +4387,11 @@
       <c r="FC5" t="inlineStr">
         <is>
           <t>O</t>
+        </is>
+      </c>
+      <c r="FD5" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="FF5" t="inlineStr">
@@ -4846,6 +4861,11 @@
           <t>O</t>
         </is>
       </c>
+      <c r="DY6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="EA6" t="inlineStr">
         <is>
           <t>N</t>
@@ -4941,6 +4961,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="FA6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="FB6" t="inlineStr">
         <is>
           <t>N</t>
@@ -4949,6 +4974,11 @@
       <c r="FC6" t="inlineStr">
         <is>
           <t>O</t>
+        </is>
+      </c>
+      <c r="FD6" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="FF6" t="inlineStr">
@@ -5418,6 +5448,11 @@
           <t>O</t>
         </is>
       </c>
+      <c r="DY7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="EA7" t="inlineStr">
         <is>
           <t>N</t>
@@ -5513,6 +5548,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="FA7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="FB7" t="inlineStr">
         <is>
           <t>N</t>
@@ -5521,6 +5561,11 @@
       <c r="FC7" t="inlineStr">
         <is>
           <t>O</t>
+        </is>
+      </c>
+      <c r="FD7" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="FF7" t="inlineStr">
@@ -5990,6 +6035,11 @@
           <t>O</t>
         </is>
       </c>
+      <c r="DY8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="EA8" t="inlineStr">
         <is>
           <t>N</t>
@@ -6085,6 +6135,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="FA8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="FB8" t="inlineStr">
         <is>
           <t>N</t>
@@ -6093,6 +6148,11 @@
       <c r="FC8" t="inlineStr">
         <is>
           <t>O</t>
+        </is>
+      </c>
+      <c r="FD8" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="FF8" t="inlineStr">
@@ -6562,6 +6622,11 @@
           <t>O</t>
         </is>
       </c>
+      <c r="DY9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="EA9" t="inlineStr">
         <is>
           <t>N</t>
@@ -6657,6 +6722,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="FA9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="FB9" t="inlineStr">
         <is>
           <t>N</t>
@@ -6665,6 +6735,11 @@
       <c r="FC9" t="inlineStr">
         <is>
           <t>O</t>
+        </is>
+      </c>
+      <c r="FD9" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="FF9" t="inlineStr">
@@ -7134,6 +7209,11 @@
           <t>O</t>
         </is>
       </c>
+      <c r="DY10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="EA10" t="inlineStr">
         <is>
           <t>N</t>
@@ -7229,6 +7309,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="FA10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="FB10" t="inlineStr">
         <is>
           <t>N</t>
@@ -7237,6 +7322,11 @@
       <c r="FC10" t="inlineStr">
         <is>
           <t>O</t>
+        </is>
+      </c>
+      <c r="FD10" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="FF10" t="inlineStr">
@@ -7706,6 +7796,11 @@
           <t>O</t>
         </is>
       </c>
+      <c r="DY11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="EA11" t="inlineStr">
         <is>
           <t>N</t>
@@ -7801,6 +7896,11 @@
           <t>N</t>
         </is>
       </c>
+      <c r="FA11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="FB11" t="inlineStr">
         <is>
           <t>N</t>
@@ -7809,6 +7909,11 @@
       <c r="FC11" t="inlineStr">
         <is>
           <t>O</t>
+        </is>
+      </c>
+      <c r="FD11" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="FF11" t="inlineStr">
